--- a/Avancado/14 - Solver.xlsx
+++ b/Avancado/14 - Solver.xlsx
@@ -1,15 +1,116 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF5B002-BAE2-4632-8910-79369E7CA79B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Plan1" sheetId="1" r:id="rId1"/>
+    <sheet name="Exercício A" sheetId="1" r:id="rId1"/>
+    <sheet name="Relatório de Respostas A" sheetId="6" r:id="rId2"/>
+    <sheet name="Exercício B" sheetId="2" r:id="rId3"/>
+    <sheet name="Relatório de Respostas B" sheetId="3" r:id="rId4"/>
+    <sheet name="Relatório de Sensibilidade B" sheetId="4" r:id="rId5"/>
+    <sheet name="Relatório de Limites B" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'Exercício A'!$A$2:$B$2</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">'Exercício B'!$B$2:$B$4</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Exercício A'!$A$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'Exercício B'!$B$2</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Exercício A'!$B$2</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'Exercício B'!$B$3</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'Exercício A'!$B$7</definedName>
+    <definedName name="solver_lhs3" localSheetId="2" hidden="1">'Exercício B'!$B$4</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">'Exercício A'!$B$8</definedName>
+    <definedName name="solver_lhs5" localSheetId="0" hidden="1">'Exercício A'!$B$9</definedName>
+    <definedName name="solver_lhs6" localSheetId="0" hidden="1">'Exercício A'!$C$14</definedName>
+    <definedName name="solver_lhs7" localSheetId="0" hidden="1">'Exercício A'!$C$14</definedName>
+    <definedName name="solver_lhs8" localSheetId="0" hidden="1">'Exercício A'!$C$14</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">5</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'Exercício A'!$B$4</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">'Exercício B'!$B$5</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">4</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">4</definedName>
+    <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel6" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel7" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel8" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">número inteiro</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">400</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">número inteiro</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">200</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">'Exercício A'!$E$12</definedName>
+    <definedName name="solver_rhs3" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">'Exercício A'!$E$13</definedName>
+    <definedName name="solver_rhs5" localSheetId="0" hidden="1">'Exercício A'!$E$14</definedName>
+    <definedName name="solver_rhs6" localSheetId="0" hidden="1">'Exercício A'!$E$14</definedName>
+    <definedName name="solver_rhs7" localSheetId="0" hidden="1">'Exercício A'!$E$14</definedName>
+    <definedName name="solver_rhs8" localSheetId="0" hidden="1">'Exercício A'!$E$14</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">10000</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+  </definedNames>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -18,9 +119,314 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="99">
+  <si>
+    <t>Quantidade de "X"</t>
+  </si>
+  <si>
+    <t>Quantidade de "Y"</t>
+  </si>
+  <si>
+    <t>Preço X</t>
+  </si>
+  <si>
+    <t>Preço Y</t>
+  </si>
+  <si>
+    <t>Lucro</t>
+  </si>
+  <si>
+    <t>Condição</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Tempo (h) gasto para</t>
+  </si>
+  <si>
+    <t>Produção (P)</t>
+  </si>
+  <si>
+    <t>Montagem (M)</t>
+  </si>
+  <si>
+    <t>Embalagem (E)</t>
+  </si>
+  <si>
+    <t>Tempo gasto por (h)</t>
+  </si>
+  <si>
+    <t>Atende a condição ?</t>
+  </si>
+  <si>
+    <t>Produção</t>
+  </si>
+  <si>
+    <t>Montagem</t>
+  </si>
+  <si>
+    <t>Embalagem</t>
+  </si>
+  <si>
+    <t>Limite</t>
+  </si>
+  <si>
+    <t>Produtos</t>
+  </si>
+  <si>
+    <t>Qd. De Caixa</t>
+  </si>
+  <si>
+    <t>Lucro por Caixa</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Celulares</t>
+  </si>
+  <si>
+    <t>Tablets</t>
+  </si>
+  <si>
+    <t>TV LED 42''</t>
+  </si>
+  <si>
+    <t>Microsoft Excel 16.0 Relatório de Respostas</t>
+  </si>
+  <si>
+    <t>Planilha: [14 - Solver.xlsx]Exercício B</t>
+  </si>
+  <si>
+    <t>Relatório Criado: 25/03/2026 20:39:13</t>
+  </si>
+  <si>
+    <t>Resultado: O Solver encontrou uma solução.  Todas as Restrições e condições de adequação foram satisfeitas.</t>
+  </si>
+  <si>
+    <t>Mecanismo do Solver</t>
+  </si>
+  <si>
+    <t>Mecanismo: GRG Não Linear</t>
+  </si>
+  <si>
+    <t>Tempo da Solução: 0,015 Segundos.</t>
+  </si>
+  <si>
+    <t>Iterações: 4 Subproblemas: 0</t>
+  </si>
+  <si>
+    <t>Opções do Solver</t>
+  </si>
+  <si>
+    <t>Tempo Máx. Ilimitado,  Iterações Ilimitado, Precision 0,000001</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Convergência 0,0001, Tamanho da População 100, Propagação Aleatória 0, Central de Derivativos</t>
+  </si>
+  <si>
+    <t>Subproblemas Máx. Ilimitado, Soluç. Máx. Núm. Inteiro Ilimitado, Tolerância de Número Inteiro 1%, Assumir Não Negativo</t>
+  </si>
+  <si>
+    <t>Célula do Objetivo (Valor de)</t>
+  </si>
+  <si>
+    <t>Célula</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Valor Original</t>
+  </si>
+  <si>
+    <t>Valor Final</t>
+  </si>
+  <si>
+    <t>Células Variáveis</t>
+  </si>
+  <si>
+    <t>Número Inteiro</t>
+  </si>
+  <si>
+    <t>Restrições</t>
+  </si>
+  <si>
+    <t>Valor da Célula</t>
+  </si>
+  <si>
+    <t>Fórmula</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Margem de Atraso</t>
+  </si>
+  <si>
+    <t>$B$5</t>
+  </si>
+  <si>
+    <t>Total Qd. De Caixa</t>
+  </si>
+  <si>
+    <t>$B$2</t>
+  </si>
+  <si>
+    <t>Celulares Qd. De Caixa</t>
+  </si>
+  <si>
+    <t>Conting.</t>
+  </si>
+  <si>
+    <t>$B$3</t>
+  </si>
+  <si>
+    <t>Tablets Qd. De Caixa</t>
+  </si>
+  <si>
+    <t>$B$4</t>
+  </si>
+  <si>
+    <t>TV LED 42'' Qd. De Caixa</t>
+  </si>
+  <si>
+    <t>$B$5=10000</t>
+  </si>
+  <si>
+    <t>Associação</t>
+  </si>
+  <si>
+    <t>$B$2&lt;=400</t>
+  </si>
+  <si>
+    <t>$B$3&gt;=200</t>
+  </si>
+  <si>
+    <t>Não-associação</t>
+  </si>
+  <si>
+    <t>$B$4&lt;=100</t>
+  </si>
+  <si>
+    <t>Microsoft Excel 16.0 Relatório de Sensibilidade</t>
+  </si>
+  <si>
+    <t>Relatório Criado: 25/03/2026 20:39:33</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Reduzido</t>
+  </si>
+  <si>
+    <t>Gradiente</t>
+  </si>
+  <si>
+    <t>Lagrange</t>
+  </si>
+  <si>
+    <t>Multiplicador</t>
+  </si>
+  <si>
+    <t>Microsoft Excel 16.0 Relatório de Limites</t>
+  </si>
+  <si>
+    <t>Relatório Criado: 25/03/2026 20:39:47</t>
+  </si>
+  <si>
+    <t>Objetivo</t>
+  </si>
+  <si>
+    <t>Variável</t>
+  </si>
+  <si>
+    <t>Inferior</t>
+  </si>
+  <si>
+    <t>Resultado</t>
+  </si>
+  <si>
+    <t>Superior</t>
+  </si>
+  <si>
+    <t>#N/D</t>
+  </si>
+  <si>
+    <t>Planilha: [14 - Solver.xlsx]Exercício A</t>
+  </si>
+  <si>
+    <t>Relatório Criado: 25/03/2026 20:39:59</t>
+  </si>
+  <si>
+    <t>Tempo da Solução: 0 Segundos.</t>
+  </si>
+  <si>
+    <t>Iterações: 0 Subproblemas: 0</t>
+  </si>
+  <si>
+    <t>Célula do Objetivo (Máx.)</t>
+  </si>
+  <si>
+    <t>Lucro Quantidade de "Y"</t>
+  </si>
+  <si>
+    <t>$A$2</t>
+  </si>
+  <si>
+    <t>$B$7</t>
+  </si>
+  <si>
+    <t>Produção Quantidade de "Y"</t>
+  </si>
+  <si>
+    <t>$B$7&lt;=$E$12</t>
+  </si>
+  <si>
+    <t>$B$8</t>
+  </si>
+  <si>
+    <t>Montagem Quantidade de "Y"</t>
+  </si>
+  <si>
+    <t>$B$8&lt;=$E$13</t>
+  </si>
+  <si>
+    <t>$B$9</t>
+  </si>
+  <si>
+    <t>Embalagem Quantidade de "Y"</t>
+  </si>
+  <si>
+    <t>$B$9&lt;=$E$14</t>
+  </si>
+  <si>
+    <t>$A$2=Número Inteiro</t>
+  </si>
+  <si>
+    <t>$B$2=Número Inteiro</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +434,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -45,14 +480,140 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="23"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="23"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="23"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="23"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,10 +891,1165 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="3" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2">
+        <v>12250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>36750</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6">
+        <f xml:space="preserve"> (E1*A2)+(E2*B2)</f>
+        <v>196000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1">
+        <f>($A$2*B12)+($B$2*C12)</f>
+        <v>49</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f>IF(INT(B7)&lt;=E12,"Sim","Não")</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1">
+        <f t="shared" ref="B8:B9" si="0">($A$2*B13)+($B$2*C13)</f>
+        <v>105</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f t="shared" ref="C8:C9" si="1">IF(INT(B8)&lt;=E13,"Sim","Não")</f>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Sim</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5">
+        <v>8.75</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5">
+        <v>5.25</v>
+      </c>
+      <c r="C13" s="5">
+        <v>21</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="5">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5">
+        <v>14</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="5">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <scenarios current="0">
+    <scenario name="teste_01_solver" count="2" user="WILCK GOMES DE OLIVEIRA" comment="Criado por WILCK GOMES DE OLIVEIRA em 3/25/2026">
+      <inputCells r="A2" val="17895697.0666667"/>
+      <inputCells r="B2" val="53687091.2"/>
+    </scenario>
+    <scenario name="Teste_02_solver" count="2" user="WILCK GOMES DE OLIVEIRA" comment="Criado por WILCK GOMES DE OLIVEIRA em 3/25/2026">
+      <inputCells r="A2" val="4"/>
+      <inputCells r="B2" val="4"/>
+    </scenario>
+  </scenarios>
+  <mergeCells count="1">
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479C7945-5264-4F80-973F-489138AD813C}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="18">
+        <v>196000</v>
+      </c>
+      <c r="E16" s="18">
+        <v>196000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="15">
+        <v>4</v>
+      </c>
+      <c r="E21" s="15">
+        <v>4</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>4</v>
+      </c>
+      <c r="E22" s="14">
+        <v>4</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="15">
+        <v>49</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" s="13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="15">
+        <v>105</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="15">
+        <v>84</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF8EA84-236C-4B11-BBDF-042403B0460E}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="5">
+        <v>400</v>
+      </c>
+      <c r="C2" s="8">
+        <v>8000</v>
+      </c>
+      <c r="D2" s="9">
+        <f>B2*C2</f>
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="5">
+        <v>9500</v>
+      </c>
+      <c r="C3" s="8">
+        <v>2000</v>
+      </c>
+      <c r="D3" s="9">
+        <f t="shared" ref="D3:D4" si="0">B3*C3</f>
+        <v>19000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="5">
+        <v>100</v>
+      </c>
+      <c r="C4" s="8">
+        <v>3000</v>
+      </c>
+      <c r="D4" s="9">
+        <f t="shared" si="0"/>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1">
+        <f>SUM(B2:B4)</f>
+        <v>10000</v>
+      </c>
+      <c r="D5" s="9">
+        <f>SUM(D2:D4)</f>
+        <v>22500000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED9B0D24-AEA1-4580-B23A-FAE7B707AC2E}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="14">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>400</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="15">
+        <v>0</v>
+      </c>
+      <c r="E22" s="15">
+        <v>9500</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="14">
+        <v>0</v>
+      </c>
+      <c r="E23" s="14">
+        <v>100</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="15">
+        <v>10000</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="15">
+        <v>400</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="15">
+        <v>9500</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="15">
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="14">
+        <v>100</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E38ADDE-D9A6-46DB-BEC9-B922E3152D98}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="13">
+        <v>400</v>
+      </c>
+      <c r="E9" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="13">
+        <v>9500</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="11">
+        <v>100</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="11">
+        <v>10000</v>
+      </c>
+      <c r="E16" s="11">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A59B3F9-B1A6-4F3B-AF19-A9461EB0194F}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="14">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="16"/>
+      <c r="C11" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="F11" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="15">
+        <v>400</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0</v>
+      </c>
+      <c r="G13" s="15">
+        <v>9600</v>
+      </c>
+      <c r="I13" s="15">
+        <v>400</v>
+      </c>
+      <c r="J13" s="15">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="15">
+        <v>9500</v>
+      </c>
+      <c r="F14" s="15">
+        <v>200</v>
+      </c>
+      <c r="G14" s="15">
+        <v>700</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="14">
+        <v>100</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>9900</v>
+      </c>
+      <c r="I15" s="14">
+        <v>100</v>
+      </c>
+      <c r="J15" s="14">
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/Avancado/14 - Solver.xlsx
+++ b/Avancado/14 - Solver.xlsx
@@ -5,110 +5,114 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-COMPLETO\Avancado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF5B002-BAE2-4632-8910-79369E7CA79B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2412C714-38F7-4D84-8FC9-902654AE5525}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercício A" sheetId="1" r:id="rId1"/>
     <sheet name="Relatório de Respostas A" sheetId="6" r:id="rId2"/>
-    <sheet name="Exercício B" sheetId="2" r:id="rId3"/>
-    <sheet name="Relatório de Respostas B" sheetId="3" r:id="rId4"/>
-    <sheet name="Relatório de Sensibilidade B" sheetId="4" r:id="rId5"/>
-    <sheet name="Relatório de Limites B" sheetId="5" r:id="rId6"/>
+    <sheet name="Relatório de Respostas 1" sheetId="7" r:id="rId3"/>
+    <sheet name="Relatório de Sensibilidade 1" sheetId="8" r:id="rId4"/>
+    <sheet name="Relatório de Limites 1" sheetId="9" r:id="rId5"/>
+    <sheet name="Exercício B" sheetId="2" r:id="rId6"/>
+    <sheet name="Relatório de Respostas B" sheetId="3" r:id="rId7"/>
+    <sheet name="Relatório de Sensibilidade B" sheetId="4" r:id="rId8"/>
+    <sheet name="Relatório de Limites B" sheetId="5" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'Exercício A'!$A$2:$B$2</definedName>
-    <definedName name="solver_adj" localSheetId="2" hidden="1">'Exercício B'!$B$2:$B$4</definedName>
+    <definedName name="solver_adj" localSheetId="5" hidden="1">'Exercício B'!$B$2:$B$4</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
-    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_drv" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_drv" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="5" hidden="1">2147483647</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Exercício A'!$A$2</definedName>
-    <definedName name="solver_lhs1" localSheetId="2" hidden="1">'Exercício B'!$B$2</definedName>
+    <definedName name="solver_lhs1" localSheetId="5" hidden="1">'Exercício B'!$B$2</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Exercício A'!$B$2</definedName>
-    <definedName name="solver_lhs2" localSheetId="2" hidden="1">'Exercício B'!$B$3</definedName>
+    <definedName name="solver_lhs2" localSheetId="5" hidden="1">'Exercício B'!$B$3</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">'Exercício A'!$B$7</definedName>
-    <definedName name="solver_lhs3" localSheetId="2" hidden="1">'Exercício B'!$B$4</definedName>
+    <definedName name="solver_lhs3" localSheetId="5" hidden="1">'Exercício B'!$B$4</definedName>
     <definedName name="solver_lhs4" localSheetId="0" hidden="1">'Exercício A'!$B$8</definedName>
     <definedName name="solver_lhs5" localSheetId="0" hidden="1">'Exercício A'!$B$9</definedName>
     <definedName name="solver_lhs6" localSheetId="0" hidden="1">'Exercício A'!$C$14</definedName>
     <definedName name="solver_lhs7" localSheetId="0" hidden="1">'Exercício A'!$C$14</definedName>
     <definedName name="solver_lhs8" localSheetId="0" hidden="1">'Exercício A'!$C$14</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
-    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
-    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">5</definedName>
-    <definedName name="solver_num" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_num" localSheetId="5" hidden="1">3</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'Exercício A'!$B$4</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">'Exercício B'!$B$5</definedName>
+    <definedName name="solver_opt" localSheetId="5" hidden="1">'Exercício B'!$B$5</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
-    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rbv" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rbv" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">4</definedName>
-    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">4</definedName>
-    <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="5" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rel3" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="5" hidden="1">1</definedName>
     <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel5" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel6" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel7" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel8" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">número inteiro</definedName>
-    <definedName name="solver_rhs1" localSheetId="2" hidden="1">400</definedName>
+    <definedName name="solver_rhs1" localSheetId="5" hidden="1">400</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">número inteiro</definedName>
-    <definedName name="solver_rhs2" localSheetId="2" hidden="1">200</definedName>
+    <definedName name="solver_rhs2" localSheetId="5" hidden="1">200</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">'Exercício A'!$E$12</definedName>
-    <definedName name="solver_rhs3" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_rhs3" localSheetId="5" hidden="1">100</definedName>
     <definedName name="solver_rhs4" localSheetId="0" hidden="1">'Exercício A'!$E$13</definedName>
     <definedName name="solver_rhs5" localSheetId="0" hidden="1">'Exercício A'!$E$14</definedName>
     <definedName name="solver_rhs6" localSheetId="0" hidden="1">'Exercício A'!$E$14</definedName>
     <definedName name="solver_rhs7" localSheetId="0" hidden="1">'Exercício A'!$E$14</definedName>
     <definedName name="solver_rhs8" localSheetId="0" hidden="1">'Exercício A'!$E$14</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_scl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="8" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
-    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="5" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="5" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
-    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="5" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_typ" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_typ" localSheetId="5" hidden="1">3</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_val" localSheetId="2" hidden="1">10000</definedName>
+    <definedName name="solver_val" localSheetId="5" hidden="1">10000</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -120,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="101">
   <si>
     <t>Quantidade de "X"</t>
   </si>
@@ -417,6 +421,12 @@
   </si>
   <si>
     <t>$B$2=Número Inteiro</t>
+  </si>
+  <si>
+    <t>Relatório Criado: 01/04/2026 20:09:55</t>
+  </si>
+  <si>
+    <t>Tempo da Solução: 0,031 Segundos.</t>
   </si>
 </sst>
 </file>
@@ -426,7 +436,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,6 +455,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="18"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -575,16 +593,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -611,6 +623,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -932,16 +959,16 @@
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <f xml:space="preserve"> (E1*A2)+(E2*B2)</f>
         <v>196000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4"/>
+      <c r="B6" s="18"/>
       <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
@@ -989,10 +1016,10 @@
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1006,16 +1033,16 @@
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="3">
         <v>8.75</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="3">
         <v>3.5</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="3">
         <v>70</v>
       </c>
     </row>
@@ -1023,16 +1050,16 @@
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="3">
         <v>5.25</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="3">
         <v>21</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="3">
         <v>105</v>
       </c>
     </row>
@@ -1040,16 +1067,16 @@
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="3">
         <v>7</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="3">
         <v>14</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="3">
         <v>84</v>
       </c>
     </row>
@@ -1086,50 +1113,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
+      <c r="A6" s="8"/>
       <c r="B6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+      <c r="A7" s="8"/>
       <c r="B7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+      <c r="A8" s="8"/>
       <c r="B8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1154,30 +1181,30 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="16">
         <v>196000</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="16">
         <v>196000</v>
       </c>
     </row>
@@ -1187,53 +1214,53 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="C21" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="13">
         <v>4</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="13">
         <v>4</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="12">
         <v>4</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>4</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="9" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1243,104 +1270,104 @@
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13">
         <v>49</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="11">
         <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="13">
         <v>105</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="13">
         <v>84</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1348,6 +1375,625 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95C350CB-C6A3-4060-B5AB-54B8898F1156}">
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="13">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13">
+        <v>400</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="13">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13">
+        <v>9500</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="12">
+        <v>0</v>
+      </c>
+      <c r="E23" s="12">
+        <v>100</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="13">
+        <v>10000</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G28" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" s="13">
+        <v>400</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="13">
+        <v>9500</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="13">
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D31" s="12">
+        <v>100</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6C9C8B3-F5B0-48CB-BAAC-9EEE2AE01D18}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="11">
+        <v>400</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="11">
+        <v>9500</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="9">
+        <v>100</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="9">
+        <v>10000</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED5F0436-1FC9-4598-A9C6-E1E6E167A3B9}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="20"/>
+      <c r="C6" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="20"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="20"/>
+      <c r="F11" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="13">
+        <v>400</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13">
+        <v>9600</v>
+      </c>
+      <c r="I13" s="13">
+        <v>400</v>
+      </c>
+      <c r="J13" s="13">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="13">
+        <v>9500</v>
+      </c>
+      <c r="F14" s="13">
+        <v>200</v>
+      </c>
+      <c r="G14" s="13">
+        <v>700</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="12">
+        <v>100</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12">
+        <v>9900</v>
+      </c>
+      <c r="I15" s="12">
+        <v>100</v>
+      </c>
+      <c r="J15" s="12">
+        <v>10000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF8EA84-236C-4B11-BBDF-042403B0460E}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1359,16 +2005,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1376,13 +2022,13 @@
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="3">
         <v>400</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>8000</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="7">
         <f>B2*C2</f>
         <v>3200000</v>
       </c>
@@ -1391,13 +2037,13 @@
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>9500</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>2000</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="7">
         <f t="shared" ref="D3:D4" si="0">B3*C3</f>
         <v>19000000</v>
       </c>
@@ -1406,13 +2052,13 @@
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>100</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>3000</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="7">
         <f t="shared" si="0"/>
         <v>300000</v>
       </c>
@@ -1425,7 +2071,7 @@
         <f>SUM(B2:B4)</f>
         <v>10000</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="7">
         <f>SUM(D2:D4)</f>
         <v>22500000</v>
       </c>
@@ -1435,7 +2081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED9B0D24-AEA1-4580-B23A-FAE7B707AC2E}">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1450,50 +2096,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
+      <c r="A6" s="8"/>
       <c r="B6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
+      <c r="A7" s="8"/>
       <c r="B7" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+      <c r="A8" s="8"/>
       <c r="B8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1518,30 +2164,30 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="10" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="14">
-        <v>0</v>
-      </c>
-      <c r="E16" s="14">
+      <c r="D16" s="12">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12">
         <v>10000</v>
       </c>
     </row>
@@ -1551,70 +2197,70 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="15">
-        <v>0</v>
-      </c>
-      <c r="E21" s="15">
+      <c r="D21" s="13">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13">
         <v>400</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="15">
-        <v>0</v>
-      </c>
-      <c r="E22" s="15">
+      <c r="D22" s="13">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13">
         <v>9500</v>
       </c>
-      <c r="F22" s="13" t="s">
+      <c r="F22" s="11" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="14">
-        <v>0</v>
-      </c>
-      <c r="E23" s="14">
+      <c r="D23" s="12">
+        <v>0</v>
+      </c>
+      <c r="E23" s="12">
         <v>100</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="9" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1624,102 +2270,102 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="10" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="13">
         <v>10000</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="13">
         <v>400</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="13">
         <v>9500</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="13">
         <v>9300</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="12">
         <v>100</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1729,7 +2375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E38ADDE-D9A6-46DB-BEC9-B922E3152D98}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1742,17 +2388,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1762,68 +2408,68 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="14" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="15" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="11">
         <v>400</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="11">
         <v>9500</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <v>100</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1833,40 +2479,40 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="15" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="9">
         <v>10000</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1875,7 +2521,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A59B3F9-B1A6-4F3B-AF19-A9461EB0194F}">
   <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1893,159 +2539,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="16"/>
+      <c r="D6" s="14"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="15" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="12">
         <v>10000</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="16"/>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="F11" s="16" t="s">
+      <c r="D11" s="14"/>
+      <c r="F11" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G12" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="15" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="13">
         <v>400</v>
       </c>
-      <c r="F13" s="15">
-        <v>0</v>
-      </c>
-      <c r="G13" s="15">
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13">
         <v>9600</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="13">
         <v>400</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="13">
         <v>10000</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="13">
         <v>9500</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="13">
         <v>200</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="13">
         <v>700</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="11" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="12">
         <v>100</v>
       </c>
-      <c r="F15" s="14">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14">
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12">
         <v>9900</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="12">
         <v>100</v>
       </c>
-      <c r="J15" s="14">
+      <c r="J15" s="12">
         <v>10000</v>
       </c>
     </row>
